--- a/reports/hackathon-2026-07-26/hackathon_report_data.xlsx
+++ b/reports/hackathon-2026-07-26/hackathon_report_data.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26 17:00 → 2026-07-27 00:30</t>
+          <t>2026-07-26 17:00 → 2026-07-27 03:30</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jul 26 22:30 → Jul 27 06:00</t>
+          <t>Jul 26 22:30 → Jul 27 09:00</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>185</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -513,7 +513,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>297 / 242 / 40</t>
+          <t>373 / 302 / 52</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>351.76</v>
+        <v>526.62</v>
       </c>
     </row>
     <row r="9">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>230</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>198 / 220</t>
+          <t>309 / 315</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>38 / 20 / 21</t>
+          <t>70 / 37 / 30</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9 / 6 / 1</t>
+          <t>53 / 26 / 10</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>970</v>
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>172</v>
+        <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>198.17</v>
+        <v>229.45</v>
       </c>
     </row>
     <row r="3">
@@ -678,13 +678,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>102.73</v>
+        <v>194.58</v>
       </c>
     </row>
     <row r="4">
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>46.61</v>
+        <v>98.33</v>
       </c>
     </row>
     <row r="5">
@@ -762,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1264,6 +1264,183 @@
         <v>27.9</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>07-27 00:30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07-27 06:00</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>42</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>39.95</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>07-27 01:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07-27 06:30</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>38</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>56.39</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>07-27 01:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07-27 07:00</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>47</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="n">
+        <v>20</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>48.28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>07-27 02:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>07-27 07:30</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>58</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H20" t="n">
+        <v>26.12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>07-27 02:30</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>07-27 08:00</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>36</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>07-27 03:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>07-27 08:30</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1275,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3769,6 +3946,573 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>07-27 00:49</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>07-27 06:19</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>siddharthsaibarla@gmail.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>guest_locked_feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>07-27 00:52</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>07-27 06:22</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ghifari.arsa@gmail.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>07-27 00:54</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>07-27 06:24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>07-27 00:59</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>07-27 06:29</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>cezeoke@umich.edu</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>guest_locked_feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>07-27 01:08</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>07-27 06:38</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>kishore.hkrish@gmail.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>07-27 01:12</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>07-27 06:42</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>anon:caadb107</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>07-27 01:20</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>07-27 06:50</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>alara.martin@gmail.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>07-27 01:25</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>07-27 06:55</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>zsslufe9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>07-27 01:29</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>07-27 06:59</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>anon:23f87ab2</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>guest_locked_feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>07-27 01:42</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>07-27 07:12</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>07-27 01:44</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>07-27 07:14</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>harshith.mannaru@manabadi.siliconandhra.org</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>guest_locked_feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>07-27 01:44</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>07-27 07:14</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>gonzalo.galvezc@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>07-27 01:46</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>07-27 07:16</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>neil_shah@my.cuesta.edu</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>07-27 01:47</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>07-27 07:17</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>hussainmahuvawala1711@gmail.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>guest_locked_feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>07-27 01:48</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>07-27 07:18</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>vivaansrivastava12@gmail.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>07-27 01:50</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>07-27 07:20</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>praniil.nagaraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>07-27 01:50</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>07-27 07:20</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>samanyu.aiprojects@gmail.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>guest_locked_feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>07-27 01:53</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>07-27 07:23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>walterchen.ca@gmail.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>07-27 01:59</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>07-27 07:29</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ayaan.chawla@gmail.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>guest_locked_feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>07-27 02:12</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>07-27 07:42</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Matthew.you.2520@gmail.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>07-27 02:15</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>07-27 07:45</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>gulianimanit@gmail.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>guest_locked_feature</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3780,7 +4524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3866,19 +4610,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>95.20999999999999</v>
+        <v>157.85</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3967,26 +4711,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nagatarunmoturi@gmail.com</t>
+          <t>Rafael Lopez</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>6.7</v>
+        <v>35.19</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -4004,32 +4748,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rafael Lopez</t>
+          <t>benjinisevich2@gmail.com</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>26.7</v>
+        <v>7.89</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -4041,7 +4785,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sahasrakokkula77@gmail.com</t>
+          <t>nagatarunmoturi@gmail.com</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -4051,16 +4795,16 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>12.17</v>
+        <v>6.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -4078,26 +4822,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>jacob.a.quion@gmail.com</t>
+          <t>sahasrakokkula77@gmail.com</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>15.21</v>
+        <v>12.17</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -4106,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -4115,7 +4859,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kshitijkumar3@gmail.com</t>
+          <t>jacob.a.quion@gmail.com</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4125,16 +4869,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>14.1</v>
+        <v>15.21</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -4143,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -4152,7 +4896,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rosekr1</t>
+          <t>kshitijkumar3@gmail.com</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -4168,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4.49</v>
+        <v>14.1</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -4180,72 +4924,72 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mborgiottitulane@gmail.com</t>
+          <t>Rosekr1</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4.81</v>
+        <v>4.49</v>
       </c>
       <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>enochfyw@gmail.com</t>
+          <t>kshitijatus@gmail.com</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>10.53</v>
+        <v>13.98</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -4254,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -4263,7 +5007,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>benjinisevich2@gmail.com</t>
+          <t>mborgiottitulane@gmail.com</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -4273,56 +5017,56 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>5.23</v>
+        <v>4.81</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>owin@owinrojas.com</t>
+          <t>stevenyang.dev@gmail.com</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>72.45</v>
+      </c>
+      <c r="G14" t="n">
         <v>3</v>
       </c>
-      <c r="D14" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>2</v>
-      </c>
-      <c r="F14" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4337,35 +5081,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>manidweepsharma1801@gmail.com</t>
+          <t>enochfyw@gmail.com</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.41</v>
+        <v>10.53</v>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -4374,26 +5118,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stevenyang.dev@gmail.com</t>
+          <t>owin@owinrojas.com</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>18.62</v>
+        <v>7.58</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -4411,32 +5155,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yujiwork@outlook.com</t>
+          <t>phongct1105@gmail.com</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4448,35 +5192,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sahilnale@icloud.com</t>
+          <t>manidweepsharma1801@gmail.com</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.18</v>
+        <v>2.41</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -4485,137 +5229,137 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mp@gmail.com</t>
+          <t>sahilnale@icloud.com</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G19" t="n">
         <v>5</v>
       </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2</v>
-      </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>philipnisevich@gmail.com</t>
+          <t>yujiwork@outlook.com</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>4</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>11.76</v>
-      </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kakanisnehil@gmail.com</t>
+          <t>rishabh.rb@icloud.com</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>8.279999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="G21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>noriaki@uni.minerva.edu</t>
+          <t>mp@gmail.com</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
         <v>4</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
       <c r="F22" t="n">
-        <v>8.1</v>
+        <v>0.03</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -4624,23 +5368,23 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>chengreric@gmail.com</t>
+          <t>philipnisevich@gmail.com</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
@@ -4649,22 +5393,22 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.11</v>
+        <v>11.76</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -4680,16 +5424,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>7.43</v>
+        <v>10.54</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -4707,7 +5451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>kewinszlezingier@gmail.com</t>
+          <t>kakanisnehil@gmail.com</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -4717,90 +5461,90 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>4.23</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>misha@mypipdev.com</t>
+          <t>noriaki@uni.minerva.edu</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>4.2</v>
+        <v>8.1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>schan119@calpoly.edu</t>
+          <t>arshmeetsodhi@gmail.com</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4.04</v>
+        <v>2.47</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -4812,13 +5556,13 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>142857tom@gmail.com</t>
+          <t>praniil.nagaraj@gmail.com</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4828,16 +5572,16 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>2.62</v>
+        <v>1.67</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -4849,38 +5593,38 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>rishabh.rb@icloud.com</t>
+          <t>chengreric@gmail.com</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>2.2</v>
+        <v>0.11</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4892,7 +5636,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ryanandnoahlee@gmail.com</t>
+          <t>kewinszlezingier@gmail.com</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -4908,7 +5652,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.24</v>
+        <v>4.23</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -4929,7 +5673,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stepodkelly@gmail.com</t>
+          <t>misha@mypipdev.com</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -4939,13 +5683,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>7.38</v>
+        <v>4.2</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -4966,7 +5710,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>amyhsieh3730@gmail.com</t>
+          <t>schan119@calpoly.edu</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -4976,16 +5720,16 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>4.04</v>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -5003,7 +5747,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>clai74@mail.ccsf.edu</t>
+          <t>142857tom@gmail.com</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -5013,22 +5757,22 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>6.08</v>
+        <v>2.62</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -5040,27 +5784,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>amberkaurtoor@gmail.com</t>
+          <t>neil_shah@my.cuesta.edu</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G34" t="n">
         <v>2</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
@@ -5071,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sohamjani8@gmail.com</t>
+          <t>Ryanandnoahlee@gmail.com</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -5087,13 +5831,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>3.18</v>
+        <v>0.24</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -5114,14 +5858,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ryanxu240@gmail.com</t>
+          <t>stepodkelly@gmail.com</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
@@ -5130,35 +5874,35 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>2.74</v>
+        <v>7.38</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cajuliawan@gmail.com</t>
+          <t>amyhsieh3730@gmail.com</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>2</v>
@@ -5167,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.13</v>
+        <v>7</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -5182,20 +5926,20 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>aneeshpradhan@acm.org</t>
+          <t>clai74@mail.ccsf.edu</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
@@ -5204,35 +5948,35 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.12</v>
+        <v>6.08</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>harshjannawar14@gmail.com</t>
+          <t>amberkaurtoor@gmail.com</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>2</v>
@@ -5241,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.11</v>
+        <v>4.11</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -5250,41 +5994,41 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>wanzelin007@gmail.com</t>
+          <t>sohamjani8@gmail.com</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>2.34</v>
+        <v>3.18</v>
       </c>
       <c r="G40" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -5293,13 +6037,13 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kshitijatus@gmail.com</t>
+          <t>atharavhedage@gmail.com</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -5309,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1.12</v>
+        <v>3.05</v>
       </c>
       <c r="G41" t="n">
         <v>4</v>
@@ -5327,44 +6071,44 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tiwari.aadi123@gmail.com</t>
+          <t>ryanxu240@gmail.com</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.86</v>
+        <v>2.74</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -5383,16 +6127,16 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
       <c r="G43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -5410,32 +6154,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>lee.anastasia.y@gmail.com</t>
+          <t>cajuliawan@gmail.com</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5447,26 +6191,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>anon:2680c3ce</t>
+          <t>aneeshpradhan@acm.org</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>4.96</v>
+        <v>0.12</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -5484,7 +6228,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ewanjedlic@gmail.com</t>
+          <t>harshjannawar14@gmail.com</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -5494,31 +6238,34 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
+      <c r="F46" t="n">
+        <v>0.11</v>
+      </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>noliversauce@gmail.com</t>
+          <t>Matthew.you.2520@gmail.com</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -5528,13 +6275,16 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
+      <c r="F47" t="n">
+        <v>3.04</v>
+      </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -5543,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -5552,7 +6302,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nityanth M</t>
+          <t>wanzelin007@gmail.com</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -5562,19 +6312,22 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
+      <c r="F48" t="n">
+        <v>2.34</v>
+      </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5586,7 +6339,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>visheshv05@gmail.com</t>
+          <t>fkw155@mun.ca</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -5596,13 +6349,16 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
+      <c r="F49" t="n">
+        <v>1.32</v>
+      </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -5620,7 +6376,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>wuyi010507@gmail.com</t>
+          <t>aakashryback@gmail.com</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -5630,13 +6386,16 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
+      <c r="F50" t="n">
+        <v>1.01</v>
+      </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -5654,41 +6413,44 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>lipeyton2006@gmail.com</t>
+          <t>tiwari.aadi123@gmail.com</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
+      <c r="F51" t="n">
+        <v>0.86</v>
+      </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>atharavhedage@gmail.com</t>
+          <t>walterchen.ca@gmail.com</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -5698,13 +6460,16 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
+      <c r="F52" t="n">
+        <v>0.77</v>
+      </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -5722,7 +6487,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>krishnadua.official@gmail.com</t>
+          <t>jczhang223@gmail.com</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -5732,13 +6497,16 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
+      <c r="F53" t="n">
+        <v>0.08</v>
+      </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -5750,13 +6518,13 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>speedytechus@gmail.com</t>
+          <t>visheshv05@gmail.com</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -5766,11 +6534,14 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
+      <c r="F54" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
@@ -5784,13 +6555,13 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yugtmath@umich.edu</t>
+          <t>lee.anastasia.y@gmail.com</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -5800,11 +6571,14 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
+      <c r="F55" t="n">
+        <v>0.04</v>
+      </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
@@ -5812,19 +6586,19 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fkw155@mun.ca</t>
+          <t>ayaan.chawla@gmail.com</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -5834,13 +6608,16 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
+      <c r="F56" t="n">
+        <v>0.03</v>
+      </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -5858,7 +6635,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bnisevich@gmail.com</t>
+          <t>anon:2680c3ce</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -5873,8 +6650,11 @@
       <c r="E57" t="n">
         <v>0</v>
       </c>
+      <c r="F57" t="n">
+        <v>12.83</v>
+      </c>
       <c r="G57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -5886,13 +6666,13 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>satwikug@gmail.com</t>
+          <t>anon:23f87ab2</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -5906,6 +6686,9 @@
       </c>
       <c r="E58" t="n">
         <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.28</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -5926,7 +6709,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kirthanamedha@gmail.com</t>
+          <t>Nityanth M</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -5942,10 +6725,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -5960,7 +6743,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>vivekajayjariwala@gmail.com</t>
+          <t>wuyi010507@gmail.com</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -5976,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -5994,7 +6777,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>mailjohnsonchris@gmail.com</t>
+          <t>lipeyton2006@gmail.com</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -6028,7 +6811,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>umarpadela@gmail.com</t>
+          <t>kishore.hkrish@gmail.com</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -6056,13 +6839,13 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>jbrendanfay@gmail.com</t>
+          <t>shaurya2007.rana@gmail.com</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -6096,7 +6879,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>gabjenkinson@gmail.com</t>
+          <t>alara.martin@gmail.com</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -6130,7 +6913,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>lmntrixgiga@gmail.com</t>
+          <t>krishnadua.official@gmail.com</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6164,7 +6947,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kho@uni.minerva.edu</t>
+          <t>speedytechus@gmail.com</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -6198,7 +6981,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>scott.simenel@gmail.com</t>
+          <t>a20200796@pucp.edu.pe</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6214,25 +6997,25 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dejiazhu@umich.edu</t>
+          <t>gonzalo.galvezc@pucp.edu.pe</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -6266,7 +7049,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>anon:3e9ad828</t>
+          <t>samanyu.aiprojects@gmail.com</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -6300,7 +7083,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>jczhang223@gmail.com</t>
+          <t>harshith.mannaru@manabadi.siliconandhra.org</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -6319,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -6334,7 +7117,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kalenakkdai@gmail.com</t>
+          <t>yugtmath@umich.edu</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -6362,13 +7145,13 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>arshmeetsodhi@gmail.com</t>
+          <t>satwikug@gmail.com</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -6402,7 +7185,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>arunachalamk058@gmail.com</t>
+          <t>kirthanamedha@gmail.com</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -6430,13 +7213,13 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>connorlai702@gmail.com</t>
+          <t>bnisevich@gmail.com</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -6452,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -6470,7 +7253,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>marambio.sebastian@gmail.com</t>
+          <t>gabjenkinson@gmail.com</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -6504,7 +7287,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>saisathvikgorle@gmail.com</t>
+          <t>mailjohnsonchris@gmail.com</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -6538,7 +7321,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kvenugop@usc.edu</t>
+          <t>anon:3e9ad828</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -6560,10 +7343,10 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -6572,7 +7355,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>nihar.manchikalapudi@gmail.com</t>
+          <t>jbrendanfay@gmail.com</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -6606,7 +7389,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>krrithik</t>
+          <t>lmntrixgiga@gmail.com</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -6622,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -6634,13 +7417,13 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>aakashryback@gmail.com</t>
+          <t>kho@uni.minerva.edu</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -6668,13 +7451,13 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ybhatia2@wisc.edu</t>
+          <t>anon:caadb107</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -6702,13 +7485,13 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>krishna.mdesai03@gmail.com</t>
+          <t>dejiazhu@umich.edu</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -6742,7 +7525,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mannycristino@gmail.com</t>
+          <t>umarpadela@gmail.com</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -6770,13 +7553,13 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>georgeceja08@gmail.com</t>
+          <t>ghifari.arsa@gmail.com</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -6810,7 +7593,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>navelan.muthusamy@gmail.com</t>
+          <t>vivekajayjariwala@gmail.com</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -6844,7 +7627,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>bhaladharesaniya02@gmail.com</t>
+          <t>scott.simenel@gmail.com</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -6872,13 +7655,13 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>abhinavmgarg@gmail.com</t>
+          <t>kalenakkdai@gmail.com</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -6912,7 +7695,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mrend1@jh.edu</t>
+          <t>connorlai702@gmail.com</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -6928,7 +7711,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -6940,13 +7723,13 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>jsshekhtm@gmail.com</t>
+          <t>marambio.sebastian@gmail.com</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -6980,7 +7763,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>neilshah684@gmail.com</t>
+          <t>arunachalamk058@gmail.com</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -7002,19 +7785,19 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>chaitanya11203@gmail.com</t>
+          <t>gulianimanit@gmail.com</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -7042,13 +7825,13 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Carol10051113@gmail.com</t>
+          <t>hussainmahuvawala1711@gmail.com</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -7082,14 +7865,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>motdharer1999@gmail.com</t>
+          <t>cezeoke@umich.edu</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
         <v>0</v>
@@ -7110,13 +7893,13 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>shaurya2007.rana@gmail.com</t>
+          <t>krrithik</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -7132,7 +7915,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -7144,6 +7927,754 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>vivaansrivastava12@gmail.com</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>saisathvikgorle@gmail.com</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ybhatia2@wisc.edu</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>siddharthsaibarla@gmail.com</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>kvenugop@usc.edu</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>2</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>zsslufe9@gmail.com</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>krishna.mdesai03@gmail.com</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>mannycristino@gmail.com</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>georgeceja08@gmail.com</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>navelan.muthusamy@gmail.com</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>nihar.manchikalapudi@gmail.com</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>bhaladharesaniya02@gmail.com</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>abhinavmgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>mrend1@jh.edu</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>jsshekhtm@gmail.com</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>neilshah684@gmail.com</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>bryanpham2024@gmail.com</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>chaitanya11203@gmail.com</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Carol10051113@gmail.com</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>motdharer1999@gmail.com</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ewanjedlic@gmail.com</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>5</v>
+      </c>
+      <c r="K116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7158,7 +8689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8064,6 +9595,150 @@
           <t>empty</t>
         </is>
       </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>07-27 06:56</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>cezeoke@umich.edu</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>07-27 07:06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>cezeoke@umich.edu</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>07-27 07:08</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>noriaki@uni.minerva.edu</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>folder_upload</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>07-27 07:30</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>noriaki@uni.minerva.edu</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>folder_upload</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>07-27 07:40</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>noriaki@uni.minerva.edu</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>folder_upload</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>07-27 07:41</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cezeoke@umich.edu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>07-27 07:56</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>noriaki@uni.minerva.edu</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>folder_upload</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>07-27 08:11</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>cezeoke@umich.edu</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>import</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8076,7 +9751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -10008,6 +11683,2584 @@
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>07-27 06:02</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>07-27 06:03</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>07-27 06:05</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Nityanth M</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>07-27 06:13</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>07-27 06:13</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>07-27 06:13</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>07-27 06:14</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>07-27 06:18</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>sahilnale@icloud.com</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>07-27 06:20</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>sahilnale@icloud.com</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>07-27 06:26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>stevenyang.dev@gmail.com</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>07-27 06:26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>07-27 06:26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>07-27 06:26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>07-27 06:30</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>stevenyang.dev@gmail.com</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>07-27 06:30</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>07-27 06:32</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>deploy_production_failed</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>07-27 06:36</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>07-27 06:36</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>07-27 06:36</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>07-27 06:37</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>07-27 06:38</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>arshmeetsodhi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>07-27 06:39</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>deploy_production_failed</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>07-27 06:42</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>07-27 06:43</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>07-27 06:43</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>07-27 06:43</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>07-27 06:44</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>deploy_production_failed</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>07-27 06:44</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>07-27 06:46</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>07-27 06:46</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>07-27 06:46</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>07-27 06:47</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>07-27 06:50</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>deploy_production_failed</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>07-27 06:51</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>07-27 06:52</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>07-27 06:53</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>07-27 06:53</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>07-27 06:53</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>deploy_production_failed</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>07-27 06:53</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>07-27 06:58</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>deploy_production_failed</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>07-27 06:59</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>07-27 07:04</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>deploy_production_failed</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>07-27 07:04</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>07-27 07:06</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>07-27 07:09</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>07-27 07:10</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>abhinavmgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>07-27 07:12</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>07-27 07:14</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>abhinavmgarg@gmail.com</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>deploy_production_failed</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>07-27 07:15</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>07-27 07:16</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_failed</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>07-27 07:17</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>07-27 07:18</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>07-27 07:18</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>07-27 07:18</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>07-27 07:19</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>07-27 07:19</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>07-27 07:21</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>stevenyang.dev@gmail.com</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>07-27 07:22</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>07-27 07:23</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>harshith.mannaru@manabadi.siliconandhra.org</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>07-27 07:23</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>07-27 07:25</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>07-27 07:26</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>07-27 07:26</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>sahilnale@icloud.com</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>07-27 07:27</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>07-27 07:27</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>sahilnale@icloud.com</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>07-27 07:27</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>07-27 07:27</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>stevenyang.dev@gmail.com</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>07-27 07:28</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>harshith.mannaru@manabadi.siliconandhra.org</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>07-27 07:28</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>enochfyw@gmail.com</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>07-27 07:29</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>sahilnale@icloud.com</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>07-27 07:29</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>07-27 07:30</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>07-27 07:31</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>umangshankar10@gmail.com</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>07-27 07:32</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>sahilnale@icloud.com</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>07-27 07:32</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>07-27 07:32</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>142857tom@gmail.com</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>07-27 07:33</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>enochfyw@gmail.com</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>07-27 07:33</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>07-27 07:34</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>sahilnale@icloud.com</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>07-27 07:35</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>07-27 07:38</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>07-27 07:38</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>tiwari.aadi123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>07-27 07:38</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>142857tom@gmail.com</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>07-27 07:38</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>noriaki@uni.minerva.edu</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>07-27 07:40</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>07-27 07:41</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>07-27 07:42</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>07-27 07:42</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>07-27 07:45</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>07-27 07:45</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>07-27 07:45</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>07-27 07:45</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>07-27 07:46</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>07-27 07:47</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>07-27 07:49</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>tiwari.aadi123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_failed</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>07-27 07:49</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>noriaki@uni.minerva.edu</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>07-27 07:49</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>07-27 07:49</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>07-27 07:50</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>07-27 07:51</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>07-27 07:52</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>tiwari.aadi123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_failed</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>07-27 07:52</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>tiwari.aadi123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>07-27 07:52</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>tiwari.aadi123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>07-27 07:56</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>tiwari.aadi123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>deploy_production_failed</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>07-27 07:56</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>tiwari.aadi123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>07-27 07:56</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>tiwari.aadi123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>07-27 07:56</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>noriaki@uni.minerva.edu</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>07-27 07:56</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>wanzelin007@gmail.com</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>07-27 07:58</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>07-27 07:58</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>harshith.mannaru@manabadi.siliconandhra.org</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>07-27 07:58</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_failed</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>07-27 07:58</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>noriaki@uni.minerva.edu</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>07-27 07:59</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>07-27 08:03</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>harshith.mannaru@manabadi.siliconandhra.org</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>07-27 08:04</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_failed</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>07-27 08:05</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_failed</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>07-27 08:05</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>07-27 08:05</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>noriaki@uni.minerva.edu</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>07-27 08:05</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>07-27 08:07</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>tiwari.aadi123@gmail.com</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_failed</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>07-27 08:07</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>kakanisnehil@gmail.com</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>07-27 08:07</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>07-27 08:09</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>justin-kang@berkeley.edu</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>07-27 08:09</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>bryanpham2024@gmail.com</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_clicked</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>07-27 08:10</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>bryanpham2024@gmail.com</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_succeeded</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>07-27 08:15</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>phongct1105@gmail.com</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_failed</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>07-27 08:19</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>07-27 08:20</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>arunachalamk058@gmail.com</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>deploy_sandbox_failed</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>07-27 08:24</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>07-27 08:28</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>deploy_production_clicked</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>07-27 08:33</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>benjinisevich2@gmail.com</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>deploy_production_succeeded</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10020,7 +14273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11154,6 +15407,231 @@
         </is>
       </c>
       <c r="E45" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>07-27 06:19</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>anon:2680c3ce</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>builder</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>07-27 06:42</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>cajuliawan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>builder</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>07-27 06:55</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>cezeoke@umich.edu</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>builder</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>07-27 06:56</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>zsslufe9@gmail.com</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>07-27 07:18</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>a20200796@pucp.edu.pe</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>builder</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>07-27 07:21</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>praniil.nagaraj@gmail.com</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>pro</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>07-27 07:21</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>harshith.mannaru@manabadi.siliconandhra.org</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>builder</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>07-27 07:27</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>mannycristino@gmail.com</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>builder</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>07-27 07:56</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>neil_shah@my.cuesta.edu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>builder</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
         <v>15</v>
       </c>
     </row>
@@ -11206,14 +15684,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>likhith11ramesh@gmail.com, justin-kang@berkeley.edu, stevenyang.dev@gmail.com, owin@owinrojas.com, mp@gmail.com, Rafael Lopez</t>
+          <t>likhith11ramesh@gmail.com, justin-kang@berkeley.edu, benjinisevich2@gmail.com, owin@owinrojas.com, stevenyang.dev@gmail.com, mp@gmail.com</t>
         </is>
       </c>
     </row>
@@ -11224,14 +15702,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>aneeshpradhan@acm.org, justin-kang@berkeley.edu, sahilnale@icloud.com, benjinisevich2@gmail.com, sahasrakokkula77@gmail.com, stevenyang.dev@gmail.com</t>
+          <t>justin-kang@berkeley.edu, benjinisevich2@gmail.com, Rosekr1, stepodkelly@gmail.com, yujiwork@outlook.com, rishabh.rb@icloud.com</t>
         </is>
       </c>
     </row>
@@ -11242,68 +15720,68 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lee.anastasia.y@gmail.com, clai74@mail.ccsf.edu, kvenugop@usc.edu, benjinisevich2@gmail.com, harshjannawar14@gmail.com, chengreric@gmail.com</t>
+          <t>lee.anastasia.y@gmail.com, clai74@mail.ccsf.edu, kvenugop@usc.edu, benjinisevich2@gmail.com, harshjannawar14@gmail.com, phongct1105@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Blocked by quota</t>
+          <t>Preview failed</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>jacob.a.quion@gmail.com, Rafael Lopez, mborgiottitulane@gmail.com, kakanisnehil@gmail.com, kewinszlezingier@gmail.com</t>
+          <t>justin-kang@berkeley.edu, sahilnale@icloud.com, phongct1105@gmail.com, harshjannawar14@gmail.com, stevenyang.dev@gmail.com, atharavhedage@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Upgrade checkout failed</t>
+          <t>Blocked by quota</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nityanth M, jczhang223@gmail.com, enochfyw@gmail.com</t>
+          <t>jacob.a.quion@gmail.com, Rafael Lopez, mborgiottitulane@gmail.com, kakanisnehil@gmail.com, praniil.nagaraj@gmail.com, kewinszlezingier@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Preview failed</t>
+          <t>Production deploy failed</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>harshjannawar14@gmail.com, sahilnale@icloud.com</t>
+          <t>benjinisevich2@gmail.com, tiwari.aadi123@gmail.com, abhinavmgarg@gmail.com, wanzelin007@gmail.com, philipnisevich@gmail.com, cajuliawan@gmail.com</t>
         </is>
       </c>
     </row>
@@ -11314,32 +15792,32 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>jacob.a.quion@gmail.com, enochfyw@gmail.com</t>
+          <t>jacob.a.quion@gmail.com, atharavhedage@gmail.com, enochfyw@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Production deploy failed</t>
+          <t>Upgrade checkout failed</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>philipnisevich@gmail.com</t>
+          <t>Nityanth M, jczhang223@gmail.com, enochfyw@gmail.com</t>
         </is>
       </c>
     </row>
@@ -11372,7 +15850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -12077,6 +16555,380 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>07-27 06:57</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>07-27 06:57</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>github_connect_succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>07-27 06:58</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>07-27 06:58</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>github_connect_succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>07-27 06:58</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>07-27 06:58</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>github_connect_succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>07-27 07:08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>07-27 07:08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>github_connect_succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>07-27 07:08</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>07-27 07:08</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>github_connect_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>07-27 07:09</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>07-27 07:09</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>github_connect_succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>07-27 07:09</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>07-27 07:09</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>07-27 07:09</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>github_connect_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>07-27 07:09</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>github_connect_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>07-27 07:24</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>07-27 07:24</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>07-27 07:24</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>github_connect_succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>07-27 07:24</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>atharavhedage@gmail.com</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>github_connect_failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>07-27 08:02</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>github_connect_clicked</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>07-27 08:02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>noliversauce@gmail.com</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>github_connect_succeeded</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
